--- a/lead_generation_forms/022_email_listing_enrollment_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/022_email_listing_enrollment_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>form category</t>
+          <t>Form Category 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>assigned tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>assigned_user</t>
+          <t>assigned_user_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>assigned user</t>
+          <t>Assigned User 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>assigned_user_choices</t>
+          <t>assigned_user_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>assigned_user_choices</t>
+          <t>assigned_user_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
